--- a/data/changelog.xlsx
+++ b/data/changelog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/pgallego_ic_ac_uk/Documents/PhD/Repositories/article-classifier/data/results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon-my.sharepoint.com/personal/pgallego_ic_ac_uk/Documents/PhD/Repositories/article-classifier/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{F01B6927-02B3-4A2F-AA04-1B6EB977945C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58F693B3-AC0F-4617-8D1C-4930451F6D8A}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{F01B6927-02B3-4A2F-AA04-1B6EB977945C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28D85CFE-D754-4F57-9B0C-D76789AD074D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Affinities" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="73">
   <si>
     <t>20260413_151017</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>4 classification prompts; claude, deepseek flash, gemma4 models; repaired; mean instead of adjudication</t>
+  </si>
+  <si>
+    <t>20260726_134607_5 with adjudicator enabled (see notebook 15)</t>
   </si>
 </sst>
 </file>
@@ -587,7 +590,7 @@
   <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="56.28515625" bestFit="1" customWidth="1"/>
   </cols>
@@ -807,6 +810,9 @@
       </c>
       <c r="B23" t="s">
         <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
